--- a/Data/StructuralAnalysis.xlsx
+++ b/Data/StructuralAnalysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/147a029199edd8ae/PG Materials/Semester3/Structural_Phylogeny/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="318" documentId="14_{1F723599-1D32-1444-9A09-B09FE5E1B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2ED507D-8CE5-2940-8A53-E689C8191861}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="14_{1F723599-1D32-1444-9A09-B09FE5E1B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{053ABB05-D87A-8347-B1EA-174EDF42D173}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29340" windowHeight="18880" activeTab="2" xr2:uid="{430A233A-6B30-984D-B0B1-B5E6015D3913}"/>
   </bookViews>
@@ -2465,7 +2465,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="9"/>
